--- a/bench/markhand_web/soak/fixtures/soak-xlsx.xlsx
+++ b/bench/markhand_web/soak/fixtures/soak-xlsx.xlsx
@@ -1,4 +1,28 @@
 
-<file path=markhand/soak-xlsx.txt>markhand soak xlsx fixture
+<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheets>
+    <sheet name="Budget" sheetId="1" r:id="rId1"/>
+  </sheets>
+</workbook>
+</file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+  <si>
+    <t>SOAKXLSX15</t>
+  </si>
+</sst>
+</file>
+
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>